--- a/docs/Contoh-JobGrade-PG-final.xlsx
+++ b/docs/Contoh-JobGrade-PG-final.xlsx
@@ -12,24 +12,22 @@
     <sheet name="job_grade" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="unit_organisasi" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="jabatan" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="jabatan_grade" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="penempatan" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="person_grade" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="jabatan_hirarki" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="vw_status_pg_jg" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="rekap (dokumen)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="penempatan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="person_grade" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="jabatan_hirarki" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="vw_status_pg_jg" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="rekap (dokumen)" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'band'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'band'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'job_grade'!$A$1:$B$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'unit_organisasi'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'jabatan'!$A$1:$I$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'jabatan_grade'!$A$1:$F$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'penempatan'!$A$1:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'person_grade'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'jabatan_hirarki'!$A$1:$E$179</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'vw_status_pg_jg'!$A$1:$F$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'rekap (dokumen)'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'jabatan'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'penempatan'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'person_grade'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'jabatan_hirarki'!$A$1:$E$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'vw_status_pg_jg'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'rekap (dokumen)'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -506,7 +504,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Band = jangkar (0=Direksi, I-VI). JG &amp; PG = transaksi per tahun (kolom tahun_berlaku). Tanpa versi SO, tanpa nomor SK.</t>
+          <t>JG MELEKAT DI JABATAN (kolom jg). band = jenjang saja (tanpa jg_min/max). job_grade = skala JG 7-21 -&gt; band.</t>
         </is>
       </c>
     </row>
@@ -516,61 +514,54 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>band, job_grade      : master jangkar (Band 0-6, skala JG 7-21).</t>
+          <t>band, job_grade      : master (Band 0-6 jenjang; skala JG 7-21 -&gt; band).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>unit_organisasi      : hierarki unit.</t>
+          <t>unit_organisasi      : hierarki unit (SO/struktur).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>jabatan              : posisi; id_band jangkar; id_atasan = atasan langsung sampai Direksi.</t>
+          <t>jabatan              : posisi; id_band=jenjang, jg=grade; id_atasan sampai Direksi.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>jabatan_grade        : JG jabatan per tahun (jg_max, tahun_berlaku).</t>
+          <t>person_grade         : PG pegawai per tahun (pg, tahun_berlaku).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>person_grade         : PG pegawai per tahun (pg, tahun_berlaku).</t>
+          <t>penempatan           : siapa mengisi jabatan mana (id_karyawan, status).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>penempatan           : siapa mengisi jabatan mana (id_karyawan, status).</t>
+          <t>jabatan_hirarki      : atasan-bawahan SEGALA TINGKAT (dibangun otomatis dari id_atasan).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>jabatan_hirarki      : atasan-bawahan SEGALA TINGKAT (dibangun otomatis dari id_atasan).</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>vw_status_pg_jg      : HASIL - status kebijakan PG&lt;=JG (baris 'dibekukan' disorot).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>vw_status_pg_jg      : HASIL - status kebijakan PG&lt;=JG (baris 'dibekukan' disorot).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>id_karyawan 'GCS-xxx' = placeholder; ganti dgn ID_KARYAWAN asli MST_PEGAWAI. Band 4-5 belum dirinci.</t>
         </is>
@@ -582,879 +573,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>id_karyawan</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>nama</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>jabatan</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>jg_jabatan</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>person_grade</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>status_kebijakan</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>GCS-016</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Nanang Budi D, SE</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Manager Kepatuhan</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>PG di atas JG - dibekukan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>GCS-017</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Joko Purwanto, SE</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Staf Madya Perencanaan, Pengendalian &amp; Produksi</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>PG di atas JG - dibekukan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>GCS-008</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>I Dewa Putu Candra K., ST</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Manager Penjualan Kesuplieran</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Ada ruang naik</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>GCS-049</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Setyo Haryono</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Staf Transport &amp; Bengkel (Junior)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Selaras (mentok di JG jabatan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>GCS-047</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Farid Fahrudin</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Staf Akuntansi &amp; Verifikasi (Junior)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Selaras (mentok di JG jabatan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>GCS-048</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Muhammad Ari Wibowo</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Staf Penjualan Kesuplieran (Junior)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Selaras (mentok di JG jabatan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>GCS-001</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Abdul Rahman, SE</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>GM Penjualan Korporasi</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>GCS-002</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Widodo</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>GM Penjualan Retail</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>GCS-003</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Moh. Faisal Alfarokhi</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>GM SDM, Kepatuhan &amp; Pengembangan</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>GCS-004</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Ach. Wachyudi</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>GM Administrasi Keuangan</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>GCS-005</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Ita Sudarwati</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Manager Penjualan Pupuk &amp; Pestisida Korporasi</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>GCS-009</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Sri Rahayu</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Manager Keuangan</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>GCS-010</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Ridlo Patyodi</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Manager Region Makassar</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>GCS-013</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Ahmad Mukhlis K.</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Manager Jasa Logistik</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>GCS-018</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Bagus Adita</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Manager Anggaran &amp; Akuntansi</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>GCS-019</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Choiri</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Manager Audit Internal</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>GCS-023</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Burnama Kusuma DR., SE</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi &amp; Non Subsidi (Jawa)</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>GCS-024</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Lilik Munawati</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penagihan</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>GCS-025</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Fifi Emmalia, SE</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Perbendaharaan</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>GCS-026</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Dwi Rini P, SE</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Pajak &amp; Asuransi</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>GCS-029</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Ardhi Yunanto</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Perijinan, Hukum &amp; K3</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>GCS-030</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Erly Nurlianti</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Sekretariat, Keamanan, Umum &amp; Manajemen Aset</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>GCS-031</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Ari Rahayu</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Pengadaan &amp; Pengelolaan Pengembangan</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>GCS-032</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Golik</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi (Lampung)</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>GCS-035</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Kusno</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pestisida (Jawa)</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>GCS-036</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Diah Puspitasari</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Administrasi &amp; Pengembangan SDM &amp; Inovasi</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>GCS-037</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Yudistira Sigit W.</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Tata Kelola, Manajemen Risiko &amp; Sistem Manajemen</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>T.211273</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Ari Kuncoro</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Teknologi Informatika &amp; Multimedia</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>GCS-039</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Wynfried Ardian Didok</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Akuntansi &amp; Verifikasi</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>GCS-040</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>M. Syamsuddin, SE</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Anggaran &amp; Pelaporan</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>GCS-041</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Widya Nanang Suryanto, ST</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Audit Internal</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F32"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1687,16 +805,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1717,20 +833,10 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>jg_min</t>
+          <t>urutan</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>jg_max</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>urutan</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>keterangan</t>
         </is>
@@ -1750,12 +856,10 @@
           <t>Direksi (Direktur Utama &amp; Direktur)</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n">
+      <c r="D2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Di atas Band I; di luar skala 7-21</t>
         </is>
@@ -1776,15 +880,9 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Pemimpin Kompartemen</t>
         </is>
@@ -1805,15 +903,9 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Pemimpin Departemen</t>
         </is>
@@ -1834,15 +926,9 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Pemimpin Bagian</t>
         </is>
@@ -1863,15 +949,9 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Analisis/teknis</t>
         </is>
@@ -1892,15 +972,9 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Eksekusi</t>
         </is>
@@ -1921,22 +995,16 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Entry level</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2265,18 +1333,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2302,25 +1371,30 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>jg</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>id_atasan</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>nama_atasan (bantu)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>jumlah_formasi</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>inti</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>kelompok_fungsi</t>
         </is>
@@ -2344,22 +1418,25 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Direktur Komersil</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Inti</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Penjualan Korporasi</t>
         </is>
@@ -2383,22 +1460,25 @@
         <v>1</v>
       </c>
       <c r="E3" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Direktur Komersil</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Inti</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Penjualan Retail</t>
         </is>
@@ -2422,22 +1502,25 @@
         <v>1</v>
       </c>
       <c r="E4" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Direktur Utama</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Pendukung</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Governance/SDM</t>
         </is>
@@ -2461,22 +1544,25 @@
         <v>1</v>
       </c>
       <c r="E5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Direktur Utama</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Pendukung</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Keuangan</t>
         </is>
@@ -2500,18 +1586,21 @@
         <v>2</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>GM Penjualan Korporasi</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Penj Korporasi</t>
         </is>
@@ -2535,18 +1624,21 @@
         <v>2</v>
       </c>
       <c r="E7" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>GM Penjualan Retail</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Retail Region</t>
         </is>
@@ -2570,18 +1662,21 @@
         <v>2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>GM Penjualan Korporasi</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Penj B3</t>
         </is>
@@ -2605,18 +1700,21 @@
         <v>2</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>GM Penjualan Korporasi</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Penj Korporasi</t>
         </is>
@@ -2640,18 +1738,21 @@
         <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>GM Administrasi Keuangan</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Keuangan</t>
         </is>
@@ -2675,18 +1776,21 @@
         <v>2</v>
       </c>
       <c r="E11" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>GM Penjualan Retail</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Retail Region</t>
         </is>
@@ -2710,18 +1814,21 @@
         <v>2</v>
       </c>
       <c r="E12" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>GM Penjualan Retail</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Penj Retail</t>
         </is>
@@ -2745,18 +1852,21 @@
         <v>2</v>
       </c>
       <c r="E13" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>GM Penjualan Retail</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Retail Region</t>
         </is>
@@ -2780,18 +1890,21 @@
         <v>2</v>
       </c>
       <c r="E14" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>GM Penjualan Retail</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Logistik</t>
         </is>
@@ -2815,18 +1928,21 @@
         <v>2</v>
       </c>
       <c r="E15" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>GM SDM, Kepatuhan &amp; Pengembangan</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Pengadaan</t>
         </is>
@@ -2850,18 +1966,21 @@
         <v>2</v>
       </c>
       <c r="E16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>GM SDM, Kepatuhan &amp; Pengembangan</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>SDM</t>
         </is>
@@ -2885,18 +2004,21 @@
         <v>2</v>
       </c>
       <c r="E17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>GM SDM, Kepatuhan &amp; Pengembangan</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Kepatuhan</t>
         </is>
@@ -2920,18 +2042,21 @@
         <v>2</v>
       </c>
       <c r="E18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Direktur Komersil</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Perencanaan</t>
         </is>
@@ -2955,18 +2080,21 @@
         <v>2</v>
       </c>
       <c r="E19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>GM Administrasi Keuangan</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Keuangan</t>
         </is>
@@ -2990,18 +2118,21 @@
         <v>2</v>
       </c>
       <c r="E20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F20" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Direktur Utama</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Audit</t>
         </is>
@@ -3025,18 +2156,21 @@
         <v>3</v>
       </c>
       <c r="E21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F21" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Manager Region Medan</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3060,18 +2194,21 @@
         <v>3</v>
       </c>
       <c r="E22" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Manager Region Medan</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3095,18 +2232,21 @@
         <v>3</v>
       </c>
       <c r="E23" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F23" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Manager Region Makassar</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3130,18 +2270,21 @@
         <v>3</v>
       </c>
       <c r="E24" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Manager Penjualan Pupuk &amp; Pestisida Retail</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3165,18 +2308,21 @@
         <v>3</v>
       </c>
       <c r="E25" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Manager Keuangan</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3200,18 +2346,21 @@
         <v>3</v>
       </c>
       <c r="E26" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Manager Keuangan</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3235,18 +2384,21 @@
         <v>3</v>
       </c>
       <c r="E27" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Manager Anggaran &amp; Akuntansi</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3270,18 +2422,21 @@
         <v>3</v>
       </c>
       <c r="E28" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Manager Jasa Logistik</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3305,18 +2460,21 @@
         <v>3</v>
       </c>
       <c r="E29" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F29" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Manager Jasa Logistik</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3340,18 +2498,21 @@
         <v>3</v>
       </c>
       <c r="E30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Manager Kepatuhan</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3377,16 +2538,19 @@
       <c r="E31" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Manager SDM</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3410,18 +2574,21 @@
         <v>3</v>
       </c>
       <c r="E32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F32" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Manager Pengembangan</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3445,18 +2612,21 @@
         <v>3</v>
       </c>
       <c r="E33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Manager Region Lampung</t>
         </is>
       </c>
-      <c r="G33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3480,18 +2650,21 @@
         <v>3</v>
       </c>
       <c r="E34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Manager Region Lampung</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3515,18 +2688,21 @@
         <v>3</v>
       </c>
       <c r="E35" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F35" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Manager Region Makassar</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3550,18 +2726,21 @@
         <v>3</v>
       </c>
       <c r="E36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F36" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Manager Penjualan Pupuk &amp; Pestisida Retail</t>
         </is>
       </c>
-      <c r="G36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3587,16 +2766,19 @@
       <c r="E37" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Manager SDM</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3620,18 +2802,21 @@
         <v>3</v>
       </c>
       <c r="E38" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F38" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Manager Kepatuhan</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3655,18 +2840,21 @@
         <v>3</v>
       </c>
       <c r="E39" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F39" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Manager Pengembangan</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3690,18 +2878,21 @@
         <v>3</v>
       </c>
       <c r="E40" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F40" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Manager Anggaran &amp; Akuntansi</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="H40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3725,18 +2916,21 @@
         <v>3</v>
       </c>
       <c r="E41" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F41" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Manager Anggaran &amp; Akuntansi</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="H41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3760,18 +2954,21 @@
         <v>3</v>
       </c>
       <c r="E42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F42" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Manager Audit Internal</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="H42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Bagian</t>
         </is>
@@ -3795,18 +2992,21 @@
         <v>6</v>
       </c>
       <c r="E43" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F43" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Bag. Akuntansi &amp; Verifikasi</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="H43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Keuangan</t>
         </is>
@@ -3830,18 +3030,21 @@
         <v>6</v>
       </c>
       <c r="E44" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F44" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Manager Penjualan Kesuplieran</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="H44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Penj Korporasi</t>
         </is>
@@ -3865,18 +3068,21 @@
         <v>6</v>
       </c>
       <c r="E45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F45" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Bag. Transport &amp; Bengkel</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="H45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Operasional</t>
         </is>
@@ -3901,11 +3107,12 @@
       </c>
       <c r="E46" s="5" t="n"/>
       <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Direksi</t>
         </is>
@@ -3928,994 +3135,32 @@
       <c r="D47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Direktur Utama</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="H47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Direksi</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I47"/>
+  <autoFilter ref="A1:J47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>id_jabatan</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>nama_jabatan</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>jg_max</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>tahun_berlaku</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>catatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>GM Penjualan Korporasi</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>GM Penjualan Retail</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>GM SDM, Kepatuhan &amp; Pengembangan</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>GM Administrasi Keuangan</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Manager Penjualan Pupuk &amp; Pestisida Korporasi</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Manager Region Medan</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Manager Penjualan Bahan Kimia &amp; Gas</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Manager Penjualan Kesuplieran</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Naik dari 17 (Rev4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Manager Keuangan</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Manager Region Makassar</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Manager Penjualan Pupuk &amp; Pestisida Retail</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Manager Region Lampung</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Manager Jasa Logistik</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Manager Pengembangan</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>KOSONG - proses promosi Ari Kuncoro</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Manager SDM</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Manager Kepatuhan</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Turun dari 18 (Rev4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Staf Madya Perencanaan, Pengendalian &amp; Produksi</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>BOD-2, lapor Direktur Komersil</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Manager Anggaran &amp; Akuntansi</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Manager Audit Internal</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi (Medan)</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan Logistik, B.Kimia, Non Subsidi &amp; Pestisida (Medan)</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi (Makassar)</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi &amp; Non Subsidi (Jawa)</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penagihan</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Perbendaharaan</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Pajak &amp; Asuransi</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Transport &amp; Bengkel</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Jasa Gudang</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Perijinan, Hukum &amp; K3</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Sekretariat, Keamanan, Umum &amp; Manajemen Aset</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Pengadaan &amp; Pengelolaan Pengembangan</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi (Lampung)</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan Logistik, Non Subsidi &amp; Pestisida (Lampung)</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan Logistik, Non Subsidi &amp; Pestisida (Makassar)</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pestisida (Jawa)</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Administrasi &amp; Pengembangan SDM &amp; Inovasi</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Tata Kelola, Manajemen Risiko &amp; Sistem Manajemen</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Teknologi Informatika &amp; Multimedia</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Akuntansi &amp; Verifikasi</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Anggaran &amp; Pelaporan</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F41" s="5" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Audit Internal</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Staf Akuntansi &amp; Verifikasi (Junior)</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Golongan lama D</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Staf Penjualan Kesuplieran (Junior)</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>Golongan lama D</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Staf Transport &amp; Bengkel (Junior)</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Golongan lama D</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F45"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5999,7 +4244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6198,7 +4443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9983,4 +8228,877 @@
   <autoFilter ref="A1:E179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id_karyawan</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>nama</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>jabatan</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>jg_jabatan</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>person_grade</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>status_kebijakan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>GCS-016</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Nanang Budi D, SE</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Manager Kepatuhan</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>PG di atas JG - dibekukan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>GCS-017</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Joko Purwanto, SE</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Staf Madya Perencanaan, Pengendalian &amp; Produksi</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>PG di atas JG - dibekukan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GCS-008</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>I Dewa Putu Candra K., ST</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Manager Penjualan Kesuplieran</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Ada ruang naik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>GCS-049</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Setyo Haryono</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Staf Transport &amp; Bengkel (Junior)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Selaras (mentok di JG jabatan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>GCS-047</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Farid Fahrudin</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Staf Akuntansi &amp; Verifikasi (Junior)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Selaras (mentok di JG jabatan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>GCS-048</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Muhammad Ari Wibowo</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Staf Penjualan Kesuplieran (Junior)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Selaras (mentok di JG jabatan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>GCS-001</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Abdul Rahman, SE</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>GM Penjualan Korporasi</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>GCS-002</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Widodo</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>GM Penjualan Retail</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>GCS-003</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Moh. Faisal Alfarokhi</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>GM SDM, Kepatuhan &amp; Pengembangan</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>GCS-004</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Ach. Wachyudi</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>GM Administrasi Keuangan</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>GCS-005</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Ita Sudarwati</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Manager Penjualan Pupuk &amp; Pestisida Korporasi</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>GCS-009</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Sri Rahayu</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Manager Keuangan</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>GCS-010</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Ridlo Patyodi</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Manager Region Makassar</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>GCS-013</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Ahmad Mukhlis K.</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Manager Jasa Logistik</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>GCS-018</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Bagus Adita</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Manager Anggaran &amp; Akuntansi</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>GCS-019</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Choiri</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Manager Audit Internal</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>GCS-023</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Burnama Kusuma DR., SE</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi &amp; Non Subsidi (Jawa)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>GCS-024</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Lilik Munawati</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Penagihan</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>GCS-025</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Fifi Emmalia, SE</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Perbendaharaan</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>GCS-026</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Dwi Rini P, SE</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Pajak &amp; Asuransi</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>GCS-029</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Ardhi Yunanto</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Perijinan, Hukum &amp; K3</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>GCS-030</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Erly Nurlianti</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Sekretariat, Keamanan, Umum &amp; Manajemen Aset</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>GCS-031</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Ari Rahayu</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Pengadaan &amp; Pengelolaan Pengembangan</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>GCS-032</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Golik</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi (Lampung)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>GCS-035</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Kusno</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Penjualan &amp; Adm Pestisida (Jawa)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>GCS-036</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Diah Puspitasari</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Administrasi &amp; Pengembangan SDM &amp; Inovasi</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>GCS-037</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Yudistira Sigit W.</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Tata Kelola, Manajemen Risiko &amp; Sistem Manajemen</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>T.211273</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Ari Kuncoro</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Teknologi Informatika &amp; Multimedia</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>GCS-039</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Wynfried Ardian Didok</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Akuntansi &amp; Verifikasi</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>GCS-040</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>M. Syamsuddin, SE</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Anggaran &amp; Pelaporan</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>GCS-041</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Widya Nanang Suryanto, ST</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Audit Internal</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F32"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/Contoh-JobGrade-PG-final.xlsx
+++ b/docs/Contoh-JobGrade-PG-final.xlsx
@@ -13,21 +13,23 @@
     <sheet name="unit_organisasi" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="jabatan" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="penempatan" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="person_grade" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="jabatan_hirarki" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="vw_status_pg_jg" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="rekap (dokumen)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="contoh_riwayat" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="person_grade" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="jabatan_hirarki" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="vw_status_pg_jg" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="rekap (dokumen)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'band'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'job_grade'!$A$1:$B$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'unit_organisasi'!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'jabatan'!$A$1:$J$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'penempatan'!$A$1:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'person_grade'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'jabatan_hirarki'!$A$1:$E$179</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'vw_status_pg_jg'!$A$1:$F$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'rekap (dokumen)'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'penempatan'!$A$1:$I$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'contoh_riwayat'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'person_grade'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'jabatan_hirarki'!$A$1:$E$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'vw_status_pg_jg'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'rekap (dokumen)'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -488,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -542,26 +544,40 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>penempatan           : siapa mengisi jabatan mana (id_karyawan, status).</t>
+          <t>penempatan           : siapa mengisi jabatan (jenis, status Aktif/Selesai).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>contoh_riwayat       : CONTOH promosi &amp; mutasi -&gt; baris lama 'Selesai' + baris baru 'Aktif' (jenis terisi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>penempatan           : siapa mengisi jabatan mana (id_karyawan, status).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>jabatan_hirarki      : atasan-bawahan SEGALA TINGKAT (dibangun otomatis dari id_atasan).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>vw_status_pg_jg      : HASIL - status kebijakan PG&lt;=JG (baris 'dibekukan' disorot).</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>id_karyawan 'GCS-xxx' = placeholder; ganti dgn ID_KARYAWAN asli MST_PEGAWAI. Band 4-5 belum dirinci.</t>
         </is>
@@ -573,6 +589,879 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id_karyawan</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>nama</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>jabatan</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>jg_jabatan</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>person_grade</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>status_kebijakan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>GCS-016</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Nanang Budi D, SE</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Manager Kepatuhan</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>PG di atas JG - dibekukan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>GCS-017</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Joko Purwanto, SE</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Staf Madya Perencanaan, Pengendalian &amp; Produksi</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>PG di atas JG - dibekukan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GCS-008</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>I Dewa Putu Candra K., ST</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Manager Penjualan Kesuplieran</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Ada ruang naik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>GCS-049</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Setyo Haryono</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Staf Transport &amp; Bengkel (Junior)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Selaras (mentok di JG jabatan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>GCS-047</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Farid Fahrudin</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Staf Akuntansi &amp; Verifikasi (Junior)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Selaras (mentok di JG jabatan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>GCS-048</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Muhammad Ari Wibowo</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Staf Penjualan Kesuplieran (Junior)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Selaras (mentok di JG jabatan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>GCS-001</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Abdul Rahman, SE</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>GM Penjualan Korporasi</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>GCS-002</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Widodo</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>GM Penjualan Retail</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>GCS-003</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Moh. Faisal Alfarokhi</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>GM SDM, Kepatuhan &amp; Pengembangan</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>GCS-004</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Ach. Wachyudi</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>GM Administrasi Keuangan</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>GCS-005</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Ita Sudarwati</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Manager Penjualan Pupuk &amp; Pestisida Korporasi</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>GCS-009</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Sri Rahayu</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Manager Keuangan</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>GCS-010</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Ridlo Patyodi</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Manager Region Makassar</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>GCS-013</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Ahmad Mukhlis K.</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Manager Jasa Logistik</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>GCS-018</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Bagus Adita</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Manager Anggaran &amp; Akuntansi</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>GCS-019</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Choiri</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Manager Audit Internal</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>GCS-023</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Burnama Kusuma DR., SE</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi &amp; Non Subsidi (Jawa)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>GCS-024</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Lilik Munawati</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Penagihan</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>GCS-025</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Fifi Emmalia, SE</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Perbendaharaan</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>GCS-026</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Dwi Rini P, SE</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Pajak &amp; Asuransi</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>GCS-029</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Ardhi Yunanto</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Perijinan, Hukum &amp; K3</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>GCS-030</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Erly Nurlianti</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Sekretariat, Keamanan, Umum &amp; Manajemen Aset</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>GCS-031</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Ari Rahayu</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Pengadaan &amp; Pengelolaan Pengembangan</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>GCS-032</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Golik</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi (Lampung)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>GCS-035</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Kusno</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Penjualan &amp; Adm Pestisida (Jawa)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>GCS-036</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Diah Puspitasari</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Administrasi &amp; Pengembangan SDM &amp; Inovasi</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>GCS-037</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Yudistira Sigit W.</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Tata Kelola, Manajemen Risiko &amp; Sistem Manajemen</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>T.211273</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Ari Kuncoro</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Teknologi Informatika &amp; Multimedia</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>GCS-039</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Wynfried Ardian Didok</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Akuntansi &amp; Verifikasi</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>GCS-040</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>M. Syamsuddin, SE</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Anggaran &amp; Pelaporan</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>GCS-041</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Widya Nanang Suryanto, ST</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Audit Internal</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>PG belum ditetapkan</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F32"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3166,16 +4055,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3206,10 +4097,20 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>jenis</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>tmt</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>tanggal_selesai</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -3239,10 +4140,16 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3272,10 +4179,16 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3305,10 +4218,16 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3338,10 +4257,16 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3371,10 +4296,16 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3404,10 +4335,16 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3437,10 +4374,16 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3470,10 +4413,16 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3503,10 +4452,16 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3536,10 +4491,16 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3569,10 +4530,16 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3602,10 +4569,16 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3635,10 +4608,16 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3668,10 +4647,16 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3701,10 +4686,16 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3734,10 +4725,16 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3767,10 +4764,16 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3800,10 +4803,16 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3833,10 +4842,16 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3866,10 +4881,16 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3899,10 +4920,16 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3932,10 +4959,16 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3965,10 +4998,16 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3998,10 +5037,16 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4031,10 +5076,16 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4064,10 +5115,16 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4097,10 +5154,16 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4130,10 +5193,16 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4163,10 +5232,16 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4196,10 +5271,16 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4229,22 +5310,291 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G32"/>
+  <autoFilter ref="A1:I32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>id_karyawan</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>nama</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>jabatan</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>jg</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>jenis</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>tmt</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>tanggal_selesai</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>T.211273</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Ari Kuncoro</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Bag. Teknologi Informatika &amp; Multimedia</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>T.211273</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Ari Kuncoro</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Manager Pengembangan</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Promosi</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>GCS-010</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Ridlo Patyodi</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Manager Region Makassar</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Pengangkatan</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>GCS-010</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Ridlo Patyodi</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Manager Region Lampung</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Mutasi</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4443,7 +5793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8228,877 +9578,4 @@
   <autoFilter ref="A1:E179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>id_karyawan</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>nama</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>jabatan</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>jg_jabatan</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>person_grade</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>status_kebijakan</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>GCS-016</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Nanang Budi D, SE</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Manager Kepatuhan</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>PG di atas JG - dibekukan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>GCS-017</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Joko Purwanto, SE</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Staf Madya Perencanaan, Pengendalian &amp; Produksi</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>PG di atas JG - dibekukan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>GCS-008</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>I Dewa Putu Candra K., ST</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Manager Penjualan Kesuplieran</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Ada ruang naik</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>GCS-049</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Setyo Haryono</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Staf Transport &amp; Bengkel (Junior)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Selaras (mentok di JG jabatan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>GCS-047</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Farid Fahrudin</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Staf Akuntansi &amp; Verifikasi (Junior)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Selaras (mentok di JG jabatan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>GCS-048</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Muhammad Ari Wibowo</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Staf Penjualan Kesuplieran (Junior)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Selaras (mentok di JG jabatan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>GCS-001</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Abdul Rahman, SE</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>GM Penjualan Korporasi</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>GCS-002</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Widodo</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>GM Penjualan Retail</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>GCS-003</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Moh. Faisal Alfarokhi</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>GM SDM, Kepatuhan &amp; Pengembangan</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>GCS-004</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Ach. Wachyudi</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>GM Administrasi Keuangan</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>GCS-005</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Ita Sudarwati</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Manager Penjualan Pupuk &amp; Pestisida Korporasi</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>GCS-009</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Sri Rahayu</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Manager Keuangan</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>GCS-010</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Ridlo Patyodi</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Manager Region Makassar</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>GCS-013</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Ahmad Mukhlis K.</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Manager Jasa Logistik</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>GCS-018</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Bagus Adita</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Manager Anggaran &amp; Akuntansi</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>GCS-019</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Choiri</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Manager Audit Internal</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>GCS-023</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Burnama Kusuma DR., SE</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi &amp; Non Subsidi (Jawa)</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>GCS-024</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Lilik Munawati</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penagihan</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>GCS-025</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Fifi Emmalia, SE</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Perbendaharaan</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>GCS-026</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Dwi Rini P, SE</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Pajak &amp; Asuransi</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>GCS-029</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Ardhi Yunanto</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Perijinan, Hukum &amp; K3</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>GCS-030</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Erly Nurlianti</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Sekretariat, Keamanan, Umum &amp; Manajemen Aset</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>GCS-031</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Ari Rahayu</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Pengadaan &amp; Pengelolaan Pengembangan</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>GCS-032</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Golik</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pupuk Subsidi (Lampung)</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>GCS-035</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Kusno</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Penjualan &amp; Adm Pestisida (Jawa)</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>GCS-036</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Diah Puspitasari</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Administrasi &amp; Pengembangan SDM &amp; Inovasi</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>GCS-037</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Yudistira Sigit W.</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Tata Kelola, Manajemen Risiko &amp; Sistem Manajemen</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>T.211273</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Ari Kuncoro</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Teknologi Informatika &amp; Multimedia</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>GCS-039</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Wynfried Ardian Didok</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Akuntansi &amp; Verifikasi</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>GCS-040</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>M. Syamsuddin, SE</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Anggaran &amp; Pelaporan</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>GCS-041</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Widya Nanang Suryanto, ST</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Bag. Audit Internal</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>PG belum ditetapkan</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F32"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>